--- a/瑞源-2025itss人员签到表.xlsx
+++ b/瑞源-2025itss人员签到表.xlsx
@@ -1004,7 +1004,7 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="20.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
